--- a/data/dividends_info_20260610.xlsx
+++ b/data/dividends_info_20260610.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>62.5099983215332</v>
+        <v>61.33000183105469</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1439769675517607</v>
+        <v>0.1467471014397201</v>
       </c>
       <c r="J2" t="n">
         <v>278</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>58.5</v>
+        <v>57.79999923706055</v>
       </c>
       <c r="I3" t="n">
-        <v>1.196581196581197</v>
+        <v>1.21107268034559</v>
       </c>
       <c r="J3" t="n">
         <v>257</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.079999923706055</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6607929570941081</v>
+        <v>0.6681514817210997</v>
       </c>
       <c r="J4" t="n">
         <v>187</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>62.5099983215332</v>
+        <v>61.33000183105469</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1439769675517607</v>
+        <v>0.1467471014397201</v>
       </c>
       <c r="J6" t="n">
         <v>187</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.095000028610229</v>
+        <v>2.075000047683716</v>
       </c>
       <c r="I7" t="n">
-        <v>3.675417610904753</v>
+        <v>3.710843288218411</v>
       </c>
       <c r="J7" t="n">
         <v>166</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.17499923706055</v>
+        <v>23.5049991607666</v>
       </c>
       <c r="I8" t="n">
-        <v>1.165048582043647</v>
+        <v>1.148691808722422</v>
       </c>
       <c r="J8" t="n">
         <v>166</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.539999961853027</v>
+        <v>5.590000152587891</v>
       </c>
       <c r="I9" t="n">
-        <v>3.610108328107348</v>
+        <v>3.577817433643719</v>
       </c>
       <c r="J9" t="n">
         <v>159</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.380000114440918</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9293680099706825</v>
+        <v>0.925925909573486</v>
       </c>
       <c r="J12" t="n">
         <v>117</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.980000019073486</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J13" t="n">
         <v>110</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.17499923706055</v>
+        <v>23.5049991607666</v>
       </c>
       <c r="I14" t="n">
-        <v>1.165048582043647</v>
+        <v>1.148691808722422</v>
       </c>
       <c r="J14" t="n">
         <v>103</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>62.5099983215332</v>
+        <v>61.33000183105469</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1439769675517607</v>
+        <v>0.1467471014397201</v>
       </c>
       <c r="J15" t="n">
         <v>103</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.679999828338623</v>
+        <v>5.639999866485596</v>
       </c>
       <c r="I16" t="n">
-        <v>5.281690300468702</v>
+        <v>5.319149062089187</v>
       </c>
       <c r="J16" t="n">
         <v>96</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.980000019073486</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J18" t="n">
         <v>54</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6.03000020980835</v>
+        <v>6.090000152587891</v>
       </c>
       <c r="I19" t="n">
-        <v>4.145936837503786</v>
+        <v>4.105090209131846</v>
       </c>
       <c r="J19" t="n">
         <v>47</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.28000020980835</v>
+        <v>4.309999942779541</v>
       </c>
       <c r="I20" t="n">
-        <v>3.27102787703529</v>
+        <v>3.248259903913439</v>
       </c>
       <c r="J20" t="n">
         <v>40</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9.640000343322754</v>
+        <v>9.607000350952148</v>
       </c>
       <c r="I21" t="n">
-        <v>2.697095339629232</v>
+        <v>2.706359847007099</v>
       </c>
       <c r="J21" t="n">
         <v>40</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.65999984741211</v>
+        <v>14.5</v>
       </c>
       <c r="I22" t="n">
-        <v>4.092769483254234</v>
+        <v>4.137931034482759</v>
       </c>
       <c r="J22" t="n">
         <v>40</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.655999898910522</v>
+        <v>3.680000066757202</v>
       </c>
       <c r="I23" t="n">
-        <v>6.017505636845323</v>
+        <v>5.978260761116315</v>
       </c>
       <c r="J23" t="n">
         <v>40</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.119999885559082</v>
+        <v>6.105000019073486</v>
       </c>
       <c r="I25" t="n">
-        <v>1.633986958659309</v>
+        <v>1.638001632884127</v>
       </c>
       <c r="J25" t="n">
         <v>40</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>18.10000038146973</v>
+        <v>18.64999961853027</v>
       </c>
       <c r="I26" t="n">
-        <v>2.07734802251683</v>
+        <v>2.016085832122022</v>
       </c>
       <c r="J26" t="n">
         <v>40</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.700000047683716</v>
+        <v>2.759999990463257</v>
       </c>
       <c r="I29" t="n">
-        <v>5.555555457440915</v>
+        <v>5.434782627474683</v>
       </c>
       <c r="J29" t="n">
         <v>33</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.5</v>
+        <v>4.610000133514404</v>
       </c>
       <c r="I31" t="n">
-        <v>1.555555555555556</v>
+        <v>1.518438133897318</v>
       </c>
       <c r="J31" t="n">
         <v>26</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>34.15000152587891</v>
+        <v>33.65000152587891</v>
       </c>
       <c r="I32" t="n">
-        <v>0.43923863337555</v>
+        <v>0.4457652100985518</v>
       </c>
       <c r="J32" t="n">
         <v>26</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5.75</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.7017544094471985</v>
       </c>
       <c r="J33" t="n">
         <v>19</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>22.97999954223633</v>
+        <v>22.89999961853027</v>
       </c>
       <c r="I34" t="n">
-        <v>1.087902545604972</v>
+        <v>1.091703074954222</v>
       </c>
       <c r="J34" t="n">
         <v>12</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>29.70000076293945</v>
+        <v>29.54999923706055</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6565656396996691</v>
+        <v>0.6598984941950117</v>
       </c>
       <c r="J35" t="n">
         <v>12</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.860000014305115</v>
+        <v>1.855000019073486</v>
       </c>
       <c r="I36" t="n">
-        <v>1.774193534741913</v>
+        <v>1.778975722948103</v>
       </c>
       <c r="J36" t="n">
         <v>12</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.204999923706055</v>
+        <v>5.210000038146973</v>
       </c>
       <c r="I37" t="n">
-        <v>5.571565883780353</v>
+        <v>5.566218769225643</v>
       </c>
       <c r="J37" t="n">
         <v>12</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.782000064849854</v>
+        <v>3.779999971389771</v>
       </c>
       <c r="I38" t="n">
-        <v>4.230565765639458</v>
+        <v>4.232804264841667</v>
       </c>
       <c r="J38" t="n">
         <v>12</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.687999963760376</v>
+        <v>2.696000099182129</v>
       </c>
       <c r="I39" t="n">
-        <v>5.156250069516579</v>
+        <v>5.140949365767692</v>
       </c>
       <c r="J39" t="n">
         <v>12</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>52.22000122070312</v>
+        <v>52.31999969482422</v>
       </c>
       <c r="I40" t="n">
-        <v>1.206434288152085</v>
+        <v>1.204128447390498</v>
       </c>
       <c r="J40" t="n">
         <v>12</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6.139999866485596</v>
+        <v>6.125</v>
       </c>
       <c r="I41" t="n">
-        <v>2.280130342741082</v>
+        <v>2.285714285714286</v>
       </c>
       <c r="J41" t="n">
         <v>12</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>17.95000076293945</v>
+        <v>18.04999923706055</v>
       </c>
       <c r="I42" t="n">
-        <v>4.345403715026188</v>
+        <v>4.321329822543658</v>
       </c>
       <c r="J42" t="n">
         <v>12</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>27.01000022888184</v>
+        <v>27.28000068664551</v>
       </c>
       <c r="I43" t="n">
-        <v>3.146982572369968</v>
+        <v>3.115835698699612</v>
       </c>
       <c r="J43" t="n">
         <v>12</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>62.5099983215332</v>
+        <v>61.33000183105469</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1439769675517607</v>
+        <v>0.1467471014397201</v>
       </c>
       <c r="J44" t="n">
         <v>12</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.450000047683716</v>
+        <v>1.460000038146973</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6896551497342619</v>
+        <v>0.6849314889533817</v>
       </c>
       <c r="J45" t="n">
         <v>12</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.323999881744385</v>
+        <v>6.368000030517578</v>
       </c>
       <c r="I46" t="n">
-        <v>2.866856473596122</v>
+        <v>2.847047725049466</v>
       </c>
       <c r="J46" t="n">
         <v>12</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>9.069999694824219</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="I47" t="n">
-        <v>2.86659326072931</v>
+        <v>2.895323087458099</v>
       </c>
       <c r="J47" t="n">
         <v>12</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10.13500022888184</v>
+        <v>10.15999984741211</v>
       </c>
       <c r="I48" t="n">
-        <v>2.73310304631893</v>
+        <v>2.726377993701995</v>
       </c>
       <c r="J48" t="n">
         <v>12</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1.049999952316284</v>
+        <v>1.054999947547913</v>
       </c>
       <c r="I49" t="n">
-        <v>1.285714344102512</v>
+        <v>1.279620916700273</v>
       </c>
       <c r="J49" t="n">
         <v>5</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.046000003814697</v>
+        <v>3.089999914169312</v>
       </c>
       <c r="I50" t="n">
-        <v>3.611293495149051</v>
+        <v>3.559870649044061</v>
       </c>
       <c r="J50" t="n">
         <v>5</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.990000009536743</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>5.351170551494067</v>
+        <v>5.333333333333334</v>
       </c>
       <c r="J52" t="n">
         <v>-2</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8600000143051147</v>
+        <v>0.8799999952316284</v>
       </c>
       <c r="I53" t="n">
-        <v>2.90697669583182</v>
+        <v>2.840909106302853</v>
       </c>
       <c r="J53" t="n">
         <v>-2</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>27.5</v>
+        <v>27.60000038146973</v>
       </c>
       <c r="I54" t="n">
-        <v>4.036363636363636</v>
+        <v>4.021739074848851</v>
       </c>
       <c r="J54" t="n">
         <v>-6</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.8769999742507935</v>
+        <v>0.8619999885559082</v>
       </c>
       <c r="I55" t="n">
-        <v>3.42075266599962</v>
+        <v>3.480278468478685</v>
       </c>
       <c r="J55" t="n">
         <v>-9</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.4830000102519989</v>
+        <v>0.4790000021457672</v>
       </c>
       <c r="I56" t="n">
-        <v>4.761904660830142</v>
+        <v>4.801670124627837</v>
       </c>
       <c r="J56" t="n">
         <v>-9</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9.680000305175781</v>
+        <v>9.760000228881836</v>
       </c>
       <c r="I58" t="n">
-        <v>2.066115637342102</v>
+        <v>2.04918027981351</v>
       </c>
       <c r="J58" t="n">
         <v>-9</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.509999990463257</v>
+        <v>2.519999980926514</v>
       </c>
       <c r="I59" t="n">
-        <v>7.171314768283262</v>
+        <v>7.142857196920313</v>
       </c>
       <c r="J59" t="n">
         <v>-16</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8.399999618530273</v>
+        <v>8.350000381469727</v>
       </c>
       <c r="I60" t="n">
-        <v>3.571428733618088</v>
+        <v>3.592814207119778</v>
       </c>
       <c r="J60" t="n">
         <v>-16</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>16.65999984741211</v>
+        <v>16.77000045776367</v>
       </c>
       <c r="I61" t="n">
-        <v>1.500600253839942</v>
+        <v>1.490757264018216</v>
       </c>
       <c r="J61" t="n">
         <v>-16</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>3.990000009536743</v>
+        <v>3.960000038146973</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7518796974510066</v>
+        <v>0.7575757502779744</v>
       </c>
       <c r="J62" t="n">
         <v>-16</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>12.80000019073486</v>
+        <v>12.64999961853027</v>
       </c>
       <c r="I64" t="n">
-        <v>4.531249932479113</v>
+        <v>4.584980375417487</v>
       </c>
       <c r="J64" t="n">
         <v>-16</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>2.247999906539917</v>
+        <v>2.233999967575073</v>
       </c>
       <c r="I65" t="n">
-        <v>4.626334711911755</v>
+        <v>4.655326835697686</v>
       </c>
       <c r="J65" t="n">
         <v>-23</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>10.47999954223633</v>
+        <v>10.53499984741211</v>
       </c>
       <c r="I66" t="n">
-        <v>2.767175693388598</v>
+        <v>2.752729038446428</v>
       </c>
       <c r="J66" t="n">
         <v>-23</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>2.095000028610229</v>
+        <v>2.075000047683716</v>
       </c>
       <c r="I67" t="n">
-        <v>3.675417610904753</v>
+        <v>3.710843288218411</v>
       </c>
       <c r="J67" t="n">
         <v>-23</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>40.59999847412109</v>
+        <v>41.04999923706055</v>
       </c>
       <c r="I68" t="n">
-        <v>4.039409018809089</v>
+        <v>3.995127967065547</v>
       </c>
       <c r="J68" t="n">
         <v>-23</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>35.29000091552734</v>
+        <v>35.31999969482422</v>
       </c>
       <c r="I69" t="n">
-        <v>5.667327707889105</v>
+        <v>5.662514205211274</v>
       </c>
       <c r="J69" t="n">
         <v>-23</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>3.121999979019165</v>
+        <v>3.128000020980835</v>
       </c>
       <c r="I70" t="n">
-        <v>3.20307497347956</v>
+        <v>3.196930924848376</v>
       </c>
       <c r="J70" t="n">
         <v>-23</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>36.56999969482422</v>
+        <v>36.68000030517578</v>
       </c>
       <c r="I71" t="n">
-        <v>0.4059611737459535</v>
+        <v>0.4047437261854422</v>
       </c>
       <c r="J71" t="n">
         <v>-23</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>11.0600004196167</v>
+        <v>11.01000022888184</v>
       </c>
       <c r="I73" t="n">
-        <v>2.712477293110238</v>
+        <v>2.724795583682451</v>
       </c>
       <c r="J73" t="n">
         <v>-23</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>86.63999938964844</v>
+        <v>87.13999938964844</v>
       </c>
       <c r="I74" t="n">
-        <v>1.20036935286989</v>
+        <v>1.193481761859576</v>
       </c>
       <c r="J74" t="n">
         <v>-23</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>44.08000183105469</v>
+        <v>43.93999862670898</v>
       </c>
       <c r="I75" t="n">
-        <v>1.588021712618997</v>
+        <v>1.593081524528096</v>
       </c>
       <c r="J75" t="n">
         <v>-23</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>58.5</v>
+        <v>57.79999923706055</v>
       </c>
       <c r="I76" t="n">
-        <v>3.760683760683761</v>
+        <v>3.806228423943284</v>
       </c>
       <c r="J76" t="n">
         <v>-23</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>10.38199996948242</v>
+        <v>10.27600002288818</v>
       </c>
       <c r="I77" t="n">
-        <v>8.283567737699329</v>
+        <v>8.36901516236361</v>
       </c>
       <c r="J77" t="n">
         <v>-23</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>12.56999969482422</v>
+        <v>12.65200042724609</v>
       </c>
       <c r="I78" t="n">
-        <v>4.455051818581856</v>
+        <v>4.426177529950438</v>
       </c>
       <c r="J78" t="n">
         <v>-23</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>9.060000419616699</v>
+        <v>9.090000152587891</v>
       </c>
       <c r="I80" t="n">
-        <v>3.311258124783752</v>
+        <v>3.300329977602817</v>
       </c>
       <c r="J80" t="n">
         <v>-23</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>2.180000066757202</v>
+        <v>2.220000028610229</v>
       </c>
       <c r="I81" t="n">
-        <v>4.954128288658833</v>
+        <v>4.864864802168965</v>
       </c>
       <c r="J81" t="n">
         <v>-23</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>90.69999694824219</v>
+        <v>90.19999694824219</v>
       </c>
       <c r="I82" t="n">
-        <v>2.271223891193222</v>
+        <v>2.283813824497192</v>
       </c>
       <c r="J82" t="n">
         <v>-23</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>15.55000019073486</v>
+        <v>15.60999965667725</v>
       </c>
       <c r="I83" t="n">
-        <v>4.823151066241604</v>
+        <v>4.804612533602358</v>
       </c>
       <c r="J83" t="n">
         <v>-23</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>14.93000030517578</v>
+        <v>14.5</v>
       </c>
       <c r="I84" t="n">
-        <v>2.009377052028586</v>
+        <v>2.068965517241379</v>
       </c>
       <c r="J84" t="n">
         <v>-23</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>50.20000076293945</v>
+        <v>49.5</v>
       </c>
       <c r="I85" t="n">
-        <v>1.693227065899806</v>
+        <v>1.717171717171717</v>
       </c>
       <c r="J85" t="n">
         <v>-23</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>35.68000030517578</v>
+        <v>35.93999862670898</v>
       </c>
       <c r="I86" t="n">
-        <v>2.382286975139678</v>
+        <v>2.365052956257818</v>
       </c>
       <c r="J86" t="n">
         <v>-23</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>70.18000030517578</v>
+        <v>70.08000183105469</v>
       </c>
       <c r="I87" t="n">
-        <v>1.852379587271283</v>
+        <v>1.855022782582076</v>
       </c>
       <c r="J87" t="n">
         <v>-23</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>6.78000020980835</v>
+        <v>6.860000133514404</v>
       </c>
       <c r="I88" t="n">
-        <v>8.849557248272713</v>
+        <v>8.746355514903142</v>
       </c>
       <c r="J88" t="n">
         <v>-23</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>6.550000190734863</v>
+        <v>6.5</v>
       </c>
       <c r="I89" t="n">
-        <v>7.175572310132548</v>
+        <v>7.230769230769231</v>
       </c>
       <c r="J89" t="n">
         <v>-23</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>5.539999961853027</v>
+        <v>5.590000152587891</v>
       </c>
       <c r="I90" t="n">
-        <v>3.610108328107348</v>
+        <v>3.577817433643719</v>
       </c>
       <c r="J90" t="n">
         <v>-23</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>24.04000091552734</v>
+        <v>24.05999946594238</v>
       </c>
       <c r="I91" t="n">
-        <v>4.159733618621054</v>
+        <v>4.156276068981334</v>
       </c>
       <c r="J91" t="n">
         <v>-23</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>23.17499923706055</v>
+        <v>23.5049991607666</v>
       </c>
       <c r="I93" t="n">
-        <v>1.165048582043647</v>
+        <v>1.148691808722422</v>
       </c>
       <c r="J93" t="n">
         <v>-23</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>9.619999885559082</v>
+        <v>9.880000114440918</v>
       </c>
       <c r="I94" t="n">
-        <v>2.07900210373419</v>
+        <v>2.024291474528161</v>
       </c>
       <c r="J94" t="n">
         <v>-23</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>8.625</v>
+        <v>8.704999923706055</v>
       </c>
       <c r="I95" t="n">
-        <v>2.782608695652174</v>
+        <v>2.757036210263661</v>
       </c>
       <c r="J95" t="n">
         <v>-23</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>21.20999908447266</v>
+        <v>21.13999938964844</v>
       </c>
       <c r="I96" t="n">
-        <v>3.724658340878197</v>
+        <v>3.736991593229833</v>
       </c>
       <c r="J96" t="n">
         <v>-23</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>5.380000114440918</v>
+        <v>5.440000057220459</v>
       </c>
       <c r="I97" t="n">
-        <v>1.728624498545469</v>
+        <v>1.709558805547474</v>
       </c>
       <c r="J97" t="n">
         <v>-23</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>34.09999847412109</v>
+        <v>33.38000106811523</v>
       </c>
       <c r="I99" t="n">
-        <v>1.026393007805028</v>
+        <v>1.04853202157121</v>
       </c>
       <c r="J99" t="n">
         <v>-23</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>6.684999942779541</v>
+        <v>6.630000114440918</v>
       </c>
       <c r="I100" t="n">
-        <v>8.291697901937885</v>
+        <v>8.360482510289398</v>
       </c>
       <c r="J100" t="n">
         <v>-23</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>2.230000019073486</v>
+        <v>2.220000028610229</v>
       </c>
       <c r="I101" t="n">
-        <v>2.690582936628342</v>
+        <v>2.702702667871647</v>
       </c>
       <c r="J101" t="n">
         <v>-23</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>14.5</v>
+        <v>14.60000038146973</v>
       </c>
       <c r="I102" t="n">
-        <v>1.379310344827586</v>
+        <v>1.369862977906763</v>
       </c>
       <c r="J102" t="n">
         <v>-23</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>5.592999935150146</v>
+        <v>5.59499979019165</v>
       </c>
       <c r="I104" t="n">
-        <v>3.397103561648788</v>
+        <v>3.395889314117236</v>
       </c>
       <c r="J104" t="n">
         <v>-23</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>10.60499954223633</v>
+        <v>10.66499996185303</v>
       </c>
       <c r="I105" t="n">
-        <v>4.073550387998432</v>
+        <v>4.050632925880861</v>
       </c>
       <c r="J105" t="n">
         <v>-23</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>26.76000022888184</v>
+        <v>27.09000015258789</v>
       </c>
       <c r="I106" t="n">
-        <v>1.644245127939542</v>
+        <v>1.624215568555348</v>
       </c>
       <c r="J106" t="n">
         <v>-23</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>6.889999866485596</v>
+        <v>6.820000171661377</v>
       </c>
       <c r="I108" t="n">
-        <v>6.821480538572701</v>
+        <v>6.891495427712083</v>
       </c>
       <c r="J108" t="n">
         <v>-23</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>54.86000061035156</v>
+        <v>55.36000061035156</v>
       </c>
       <c r="I109" t="n">
-        <v>2.551950390856965</v>
+        <v>2.528901706222559</v>
       </c>
       <c r="J109" t="n">
         <v>-23</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>3.361999988555908</v>
+        <v>3.369999885559082</v>
       </c>
       <c r="I110" t="n">
-        <v>8.923259994681322</v>
+        <v>8.902077453638551</v>
       </c>
       <c r="J110" t="n">
         <v>-23</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>15.80000019073486</v>
+        <v>15.75</v>
       </c>
       <c r="I111" t="n">
-        <v>0.7594936617175999</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="J111" t="n">
         <v>-23</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>3.349999904632568</v>
+        <v>3.440000057220459</v>
       </c>
       <c r="I112" t="n">
-        <v>5.074627010135566</v>
+        <v>4.941860382914093</v>
       </c>
       <c r="J112" t="n">
         <v>-23</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>21.64999961853027</v>
+        <v>22.64999961853027</v>
       </c>
       <c r="I113" t="n">
-        <v>3.23325640800875</v>
+        <v>3.090507778319433</v>
       </c>
       <c r="J113" t="n">
         <v>-23</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>2.640000104904175</v>
+        <v>2.779999971389771</v>
       </c>
       <c r="I114" t="n">
-        <v>1.325757523076705</v>
+        <v>1.258992818712257</v>
       </c>
       <c r="J114" t="n">
         <v>-23</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>5.579999923706055</v>
+        <v>5.590000152587891</v>
       </c>
       <c r="I115" t="n">
-        <v>5.913978575484007</v>
+        <v>5.903398765512136</v>
       </c>
       <c r="J115" t="n">
         <v>-23</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>0.9369999766349792</v>
+        <v>0.9629999995231628</v>
       </c>
       <c r="I116" t="n">
-        <v>7.470651200162136</v>
+        <v>7.268951197784119</v>
       </c>
       <c r="J116" t="n">
         <v>-23</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>100</v>
+        <v>101.3000030517578</v>
       </c>
       <c r="I118" t="n">
-        <v>1.35</v>
+        <v>1.332675181964443</v>
       </c>
       <c r="J118" t="n">
         <v>-23</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>7.260000228881836</v>
+        <v>7.179999828338623</v>
       </c>
       <c r="I119" t="n">
-        <v>1.101928339915788</v>
+        <v>1.114206154772446</v>
       </c>
       <c r="J119" t="n">
         <v>-23</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>4.410999774932861</v>
+        <v>4.425000190734863</v>
       </c>
       <c r="I121" t="n">
-        <v>3.85400155688259</v>
+        <v>3.841807744007531</v>
       </c>
       <c r="J121" t="n">
         <v>-23</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>62</v>
+        <v>60.70000076293945</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7258064516129032</v>
+        <v>0.7413508967774984</v>
       </c>
       <c r="J123" t="n">
         <v>-23</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>5.639999866485596</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="I124" t="n">
-        <v>0.709219874945225</v>
+        <v>0.7017544094471985</v>
       </c>
       <c r="J124" t="n">
         <v>-23</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>37.63999938964844</v>
+        <v>37.13999938964844</v>
       </c>
       <c r="I125" t="n">
-        <v>2.789585592524653</v>
+        <v>2.827140595733702</v>
       </c>
       <c r="J125" t="n">
         <v>-23</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>16.34000015258789</v>
+        <v>16.14999961853027</v>
       </c>
       <c r="I127" t="n">
-        <v>2.325581373631851</v>
+        <v>2.35294123204804</v>
       </c>
       <c r="J127" t="n">
         <v>-23</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>26.42000007629395</v>
+        <v>26.68000030517578</v>
       </c>
       <c r="I128" t="n">
-        <v>2.271006806462375</v>
+        <v>2.248875536495414</v>
       </c>
       <c r="J128" t="n">
         <v>-23</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>36.90000152587891</v>
+        <v>36.79999923706055</v>
       </c>
       <c r="I129" t="n">
-        <v>0.9485094458723426</v>
+        <v>0.9510869762397222</v>
       </c>
       <c r="J129" t="n">
         <v>-23</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>3.160000085830688</v>
+        <v>3.240000009536743</v>
       </c>
       <c r="I130" t="n">
-        <v>0.5379746689320455</v>
+        <v>0.5246913564802943</v>
       </c>
       <c r="J130" t="n">
         <v>-23</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>23.11000061035156</v>
+        <v>23.19000053405762</v>
       </c>
       <c r="I132" t="n">
-        <v>4.846386717524894</v>
+        <v>4.829667849102161</v>
       </c>
       <c r="J132" t="n">
         <v>-23</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>2.220000028610229</v>
+        <v>2.288000106811523</v>
       </c>
       <c r="I135" t="n">
-        <v>4.157657604075883</v>
+        <v>4.034090720766007</v>
       </c>
       <c r="J135" t="n">
         <v>-23</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>9.140000343322754</v>
+        <v>9.239999771118164</v>
       </c>
       <c r="I136" t="n">
-        <v>3.829321519180174</v>
+        <v>3.787878881707432</v>
       </c>
       <c r="J136" t="n">
         <v>-30</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>6.150000095367432</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I137" t="n">
-        <v>1.560975585550206</v>
+        <v>1.655172359362229</v>
       </c>
       <c r="J137" t="n">
         <v>-30</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>6.25</v>
+        <v>6.099999904632568</v>
       </c>
       <c r="I138" t="n">
-        <v>4.8</v>
+        <v>4.918032863773797</v>
       </c>
       <c r="J138" t="n">
         <v>-30</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>11</v>
+        <v>10.80000019073486</v>
       </c>
       <c r="I139" t="n">
-        <v>1.818181818181818</v>
+        <v>1.851851819146972</v>
       </c>
       <c r="J139" t="n">
         <v>-30</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>9.079999923706055</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="I140" t="n">
-        <v>0.6607929570941081</v>
+        <v>0.6681514817210997</v>
       </c>
       <c r="J140" t="n">
         <v>-30</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>18.76000022888184</v>
+        <v>19.97999954223633</v>
       </c>
       <c r="I141" t="n">
-        <v>2.665245170041247</v>
+        <v>2.502502559837576</v>
       </c>
       <c r="J141" t="n">
         <v>-30</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>2.240000009536743</v>
+        <v>2.220000028610229</v>
       </c>
       <c r="I142" t="n">
-        <v>2.678571417167479</v>
+        <v>2.702702667871647</v>
       </c>
       <c r="J142" t="n">
         <v>-30</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>15.30000019073486</v>
+        <v>15.34000015258789</v>
       </c>
       <c r="I143" t="n">
-        <v>3.267973815469507</v>
+        <v>3.259452379572819</v>
       </c>
       <c r="J143" t="n">
         <v>-30</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>3.920000076293945</v>
+        <v>3.740000009536743</v>
       </c>
       <c r="I144" t="n">
-        <v>2.551020358513417</v>
+        <v>2.673796784625852</v>
       </c>
       <c r="J144" t="n">
         <v>-30</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>3.150000095367432</v>
+        <v>3.180000066757202</v>
       </c>
       <c r="I145" t="n">
-        <v>3.492063386339963</v>
+        <v>3.459119424238636</v>
       </c>
       <c r="J145" t="n">
         <v>-30</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>4.789999961853027</v>
+        <v>4.519999980926514</v>
       </c>
       <c r="I147" t="n">
-        <v>1.983298554416876</v>
+        <v>2.101769920373469</v>
       </c>
       <c r="J147" t="n">
         <v>-30</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>8.600000381469727</v>
+        <v>8.5</v>
       </c>
       <c r="I149" t="n">
-        <v>1.04651158148692</v>
+        <v>1.058823529411765</v>
       </c>
       <c r="J149" t="n">
         <v>-30</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>8.5</v>
+        <v>8.550000190734863</v>
       </c>
       <c r="I150" t="n">
-        <v>1.176470588235294</v>
+        <v>1.169590617183426</v>
       </c>
       <c r="J150" t="n">
         <v>-30</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>7.170000076293945</v>
+        <v>7.239999771118164</v>
       </c>
       <c r="I151" t="n">
-        <v>3.068340274184688</v>
+        <v>3.038674129212336</v>
       </c>
       <c r="J151" t="n">
         <v>-30</v>
@@ -7549,7 +7549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C115"/>
+  <dimension ref="A1:C105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7640,7 +7640,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -7650,14 +7650,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -7667,14 +7667,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -7684,14 +7684,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -7701,14 +7701,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -7718,14 +7718,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7742,7 +7742,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7752,14 +7752,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7769,14 +7769,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7810,7 +7810,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7827,7 +7827,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7837,14 +7837,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7854,14 +7854,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7871,14 +7871,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7895,7 +7895,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -7905,14 +7905,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7922,14 +7922,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7939,14 +7939,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7963,7 +7963,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -7980,7 +7980,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -7990,14 +7990,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -8007,14 +8007,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8048,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -8058,14 +8058,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8075,14 +8075,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8092,14 +8092,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8109,14 +8109,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -8126,14 +8126,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -8150,7 +8150,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -8167,7 +8167,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -8177,14 +8177,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -8201,7 +8201,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -8211,14 +8211,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -8252,7 +8252,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8269,7 +8269,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8286,7 +8286,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8296,14 +8296,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -8320,7 +8320,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -8330,14 +8330,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -8347,14 +8347,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -8371,7 +8371,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -8381,14 +8381,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -8405,7 +8405,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -8422,7 +8422,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Giocamondo Study S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -8432,14 +8432,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Giocamondo Study S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -8449,14 +8449,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -8466,14 +8466,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -8490,7 +8490,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -8507,7 +8507,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -8517,14 +8517,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8541,7 +8541,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -8551,14 +8551,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TALEA GROUP</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -8575,7 +8575,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -8592,12 +8592,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8609,12 +8609,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8626,12 +8626,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8643,12 +8643,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -8660,12 +8660,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -8677,12 +8677,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -8694,12 +8694,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -8711,12 +8711,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -8728,12 +8728,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -8745,7 +8745,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>Cyberoo S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8755,14 +8755,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8779,7 +8779,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8796,7 +8796,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8813,7 +8813,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8830,7 +8830,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8847,7 +8847,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8864,7 +8864,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8881,46 +8881,46 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cyberoo S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8932,12 +8932,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -8949,46 +8949,46 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>I GRANDI VIAGGI S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -9000,29 +9000,29 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9034,24 +9034,24 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>Cyberoo S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9061,14 +9061,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9085,7 +9085,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9095,14 +9095,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9119,46 +9119,46 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>I GRANDI VIAGGI S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -9170,46 +9170,46 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Cyberoo S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -9221,287 +9221,117 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>CleanBnB S.p.A.</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>BORGOSESIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>DOTSTAY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>FOPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>LU-VE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Otofarma S.p.A.</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Growens S.p.A.</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
         <is>
           <t>Half Year Preliminary Results</t>
         </is>
@@ -9531,180 +9361,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CIRCLE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Datrix S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Datrix S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Datrix S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Growens S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Indel B S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-06-11</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Officina Stellare S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Portobello S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>